--- a/data/raw/industry_cr_hhi.xlsx
+++ b/data/raw/industry_cr_hhi.xlsx
@@ -1,100 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
-  <si>
-    <t>季度</t>
-  </si>
-  <si>
-    <t>CR3</t>
-  </si>
-  <si>
-    <t>CR5</t>
-  </si>
-  <si>
-    <t>CR10</t>
-  </si>
-  <si>
-    <t>HHI</t>
-  </si>
-  <si>
-    <t>HHI标准化</t>
-  </si>
-  <si>
-    <t>Top1行业</t>
-  </si>
-  <si>
-    <t>Top1比例</t>
-  </si>
-  <si>
-    <t>行业数</t>
-  </si>
-  <si>
-    <t>2024Q1</t>
-  </si>
-  <si>
-    <t>2024Q2</t>
-  </si>
-  <si>
-    <t>2024Q3</t>
-  </si>
-  <si>
-    <t>2024Q4</t>
-  </si>
-  <si>
-    <t>2025Q1</t>
-  </si>
-  <si>
-    <t>2025Q2</t>
-  </si>
-  <si>
-    <t>2025Q3</t>
-  </si>
-  <si>
-    <t>2025Q4</t>
-  </si>
-  <si>
-    <t>2026Q1</t>
-  </si>
-  <si>
-    <t>2026Q2</t>
-  </si>
-  <si>
-    <t>食品饮料</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -113,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -407,330 +408,425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>季度</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>CR3</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CR5</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CR10</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>HHI</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>HHI标准化</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Top1行业</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Top1比例</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>行业数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>37.12782124475583</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>54.08395017979873</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>75.10432123708368</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.0751985956910379</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>0.0443718822140725</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>13.19659416964225</v>
       </c>
-      <c r="I2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
+      <c r="I2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>37.1683432405973</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>52.72091538553118</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>74.96051083608334</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0.07574741770337012</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>0.04493899829348246</v>
       </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>15.88123501625284</v>
       </c>
-      <c r="I3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
+      <c r="I3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>35.30656818198231</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>49.20521820630328</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>71.35154169049314</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0.06780147834299602</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.03672819428776256</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>13.66640499517099</v>
       </c>
-      <c r="I4">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
+      <c r="I4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>37.79184693546224</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>51.73728200988008</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>72.10948041667098</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.07434709176119135</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>0.04349199481989773</v>
       </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>17.04731542122867</v>
       </c>
-      <c r="I5">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
+      <c r="I5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>37.41253491174226</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>52.5964486867991</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>74.00479332859578</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0.07796903201611244</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>0.04723466641664952</v>
       </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>18.37482077291716</v>
       </c>
-      <c r="I6">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
+      <c r="I6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>38.34468442540493</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>50.07649808296888</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>73.1694146821942</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0.07699898020868653</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>0.04623227954897609</v>
       </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>18.08780491635557</v>
       </c>
-      <c r="I7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8">
+      <c r="I7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>48.07891112027485</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>63.41865968265186</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>82.2802416878948</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>0.1142777525973126</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>0.08475367768388971</v>
       </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>25.78627905739986</v>
       </c>
-      <c r="I8">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
+      <c r="I8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>46.78952840106125</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>62.95347484715536</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>82.87284891821001</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>0.1076811487195125</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>0.0779371870101629</v>
       </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>24.07652935589194</v>
       </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
+      <c r="I9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>48.03075228716249</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>63.48678858358662</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>83.31101446264037</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0.1050653079576544</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>0.07523415155624291</v>
       </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>22.13227508406082</v>
       </c>
-      <c r="I10">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
+      <c r="I10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>67.53129995312817</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>79.15423539339983</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>90.25290032698899</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>0.2313663849637868</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>0.2057452644625797</v>
       </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>43.23956375677275</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>61.226684</v>
+      </c>
+      <c r="C12" t="n">
+        <v>72.632589</v>
+      </c>
+      <c r="D12" t="n">
+        <v>86.22983799999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1782059480056407</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1508128129391621</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>36.671006</v>
+      </c>
+      <c r="I12" t="n">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>